--- a/てきword.xlsx
+++ b/てきword.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="145">
   <si>
     <t>逆に</t>
   </si>
@@ -455,6 +455,18 @@
   </si>
   <si>
     <t>だんぞくてき</t>
+  </si>
+  <si>
+    <t>実践的</t>
+  </si>
+  <si>
+    <t>じっせんてき</t>
+  </si>
+  <si>
+    <t>宿命的</t>
+  </si>
+  <si>
+    <t>しゅくめいてき</t>
   </si>
 </sst>
 </file>
@@ -467,7 +479,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -480,13 +492,6 @@
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -936,148 +941,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1403,7 +1408,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="1"/>
@@ -1929,6 +1934,22 @@
         <v>140</v>
       </c>
     </row>
+    <row r="42" spans="4:5">
+      <c r="D42" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="4:5">
+      <c r="D43" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
